--- a/Model Evaluation Data/Task data from Open FinLLMs.xlsx
+++ b/Model Evaluation Data/Task data from Open FinLLMs.xlsx
@@ -8,6 +8,19 @@
     <sheet state="visible" name="Sheet3" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId7"/>
     <sheet state="visible" name="Sheet5" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Sheet6" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="Sheet7" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="Sheet8" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="Sheet9" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="Sheet10" sheetId="10" r:id="rId13"/>
+    <sheet state="visible" name="Sheet11" sheetId="11" r:id="rId14"/>
+    <sheet state="visible" name="Sheet12" sheetId="12" r:id="rId15"/>
+    <sheet state="visible" name="Sheet13" sheetId="13" r:id="rId16"/>
+    <sheet state="visible" name="Sheet14" sheetId="14" r:id="rId17"/>
+    <sheet state="visible" name="Sheet15" sheetId="15" r:id="rId18"/>
+    <sheet state="visible" name="Sheet16" sheetId="16" r:id="rId19"/>
+    <sheet state="visible" name="Sheet17" sheetId="17" r:id="rId20"/>
+    <sheet state="visible" name="Sheet18" sheetId="18" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="362">
   <si>
     <t>meta-llama/Llama-3.2-3B-Instruct</t>
   </si>
@@ -41,7 +54,7 @@
     <t>SC</t>
   </si>
   <si>
-    <t>acc: 0.8609 ± 0.0037; missing: 0.0008 ± 0.0003; f1: 0.8725; macro_f1: 0.5327; mcc: 0.0704</t>
+    <t>acc: 0.8609  ± 0.0037; missing: 0.0008  ± 0.0003; f1: 0.8725; macro_f1: 0.5327; mcc: 0.0704</t>
   </si>
   <si>
     <t>CD</t>
@@ -65,19 +78,19 @@
     <t>FPB</t>
   </si>
   <si>
-    <t>acc: 0.6918 ± 0.0148; missing: 0.0000 ± 0.0000; f1: 0.6393; macro_f1: 0.6105; mcc: 0.4111</t>
+    <t>acc: 0.6918  ± 0.0148; missing: 0.0000  ± 0.0000; f1: 0.6393; macro_f1: 0.6105; mcc: 0.4111</t>
   </si>
   <si>
     <t>FiQA-SA</t>
   </si>
   <si>
-    <t>acc: 0.7191 ± 0.0294; missing: 0.0000 ± 0.0000; f1: 0.7438; macro_f1: 0.5897; mcc: 0.5200</t>
+    <t>acc: 0.7191  ± 0.0294; missing: 0.0000  ± 0.0000; f1: 0.7438; macro_f1: 0.5897; mcc: 0.5200</t>
   </si>
   <si>
     <t>TSA</t>
   </si>
   <si>
-    <t>rmse: 0.1645; missing: 0.0143 ± 0.005</t>
+    <t>rmse: 0.1645; missing: 0.0143  ± 0.005</t>
   </si>
   <si>
     <t>Headlines</t>
@@ -89,427 +102,1018 @@
     <t>FOMC</t>
   </si>
   <si>
-    <t>acc: 0.5101 ± 0.0225; missing: 0.0040 ± 0.0028; f1: 0.4353; macro_f1: 0.3651; mcc: 0.1612</t>
+    <t>acc: 0.5101  ± 0.0225; missing: 0.0040  ± 0.0028; f1: 0.4353; macro_f1: 0.3651; mcc: 0.1612</t>
   </si>
   <si>
     <t>FinArg-ACC</t>
   </si>
   <si>
-    <t>acc: 0.4551 ± 0.0160; missing: 0.0650 ± 0.0079; f1: 0.4283; macro_f1: 0.4354; mcc: -0.0002</t>
+    <t>acc: 0.4551  ± 0.0160; missing: 0.0650  ± 0.0079; f1: 0.4283; macro_f1: 0.4354; mcc: -0.0002</t>
   </si>
   <si>
     <t>FinArg-ARC</t>
   </si>
   <si>
-    <t>acc: 0.4536 ± 0.019; missing: 0.0000 ± 0.000; f1: 0.4888; macro_f1: 0.2656; mcc: -0.0052</t>
+    <t>acc: 0.4536  ± 0.019; missing: 0.0000  ± 0.000; f1: 0.4888; macro_f1: 0.2656; mcc: -0.0052</t>
   </si>
   <si>
     <t>MultiFin</t>
   </si>
   <si>
-    <t>acc: 0.4249 ± 0.0212; missing: 0.0018 ± 0.0018; f1: 0.3943; macro_f1: 0.3720; mcc: 0.3014</t>
+    <t>acc: 0.4249  ± 0.0212; missing: 0.0018  ± 0.0018; f1: 0.3943; macro_f1: 0.3720; mcc: 0.3014</t>
   </si>
   <si>
     <t>MA</t>
   </si>
   <si>
-    <t>acc: 0.6900 ± 0.0207; missing: 0.0000 ± 0.0000; f1: 0.6707; macro_f1: 0.6707; mcc: 0.4343</t>
+    <t>acc: 0.6900  ± 0.0207; missing: 0.0000  ± 0.0000; f1: 0.6707; macro_f1: 0.6707; mcc: 0.4343</t>
   </si>
   <si>
     <t>MLESG</t>
   </si>
   <si>
-    <t>acc: 0.3300 ± 0.0272; missing: 0.0200 ± 0.0081; f1: 0.2993; macro_f1: 0.2520; mcc: 0.3050</t>
+    <t>acc: 0.3300  ± 0.0272; missing: 0.0200  ± 0.0081; f1: 0.2993; macro_f1: 0.2520; mcc: 0.3050</t>
   </si>
   <si>
     <t>FinQA</t>
   </si>
   <si>
+    <t>acc: 0  ± 0</t>
+  </si>
+  <si>
+    <t>TATQA</t>
+  </si>
+  <si>
+    <t>acc: 0.0036  ± 0.0015</t>
+  </si>
+  <si>
+    <t>Regulations</t>
+  </si>
+  <si>
+    <t>ConvFinQA</t>
+  </si>
+  <si>
+    <t>EDTSUM</t>
+  </si>
+  <si>
+    <t>Can't get BARTScore; unpickling error</t>
+  </si>
+  <si>
+    <t>ECTSUM</t>
+  </si>
+  <si>
+    <t>BigData22</t>
+  </si>
+  <si>
+    <t>acc: 0.4674  ± 0.013; missing: 0.0000  ± 0.000; f1: 0.3794; macro_f1: 0.4004; mcc: 0.0248</t>
+  </si>
+  <si>
+    <t>ACL18</t>
+  </si>
+  <si>
+    <t>acc: 0.4978  ± 0.0082; missing: 0.0000  ± 0.0000; f1: 0.4915; macro_f1: 0.4928; mcc: 0.0015</t>
+  </si>
+  <si>
+    <t>CIKM18</t>
+  </si>
+  <si>
+    <t>acc: 0.5241  ± 0.0148; missing: 0.0000  ± 0.0000; f1: 0.5194; macro_f1: 0.5027; mcc: 0.0075</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>acc: 0.3950  ± 0.0347; missing: 0.0000  ± 0.0000; f1: 0.3270; macro_f1: 0.3685; mcc: 0.0364</t>
+  </si>
+  <si>
+    <t>Australian</t>
+  </si>
+  <si>
+    <t>acc: 0.4317  ± 0.0422; missing: 0.0000  ± 0.0000; f1: 0.2603; macro_f1: 0.3015; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>LendingClub</t>
+  </si>
+  <si>
+    <t>acc: 0.1918  ± 0.0076; missing: 0.0000  ± 0.0000; f1: 0.0617; macro_f1: 0.1609; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>ccf</t>
+  </si>
+  <si>
+    <t>acc: 0.9987  ± 0.0008; missing: 0.0000  ± 0.0000; f1: 0.9980; macro_f1: 0.4997; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>ccfraud</t>
+  </si>
+  <si>
+    <t>acc: 0.0586  ± 0.0051; missing: 0.0000  ± 0.0000; f1: 0.0065; macro_f1: 0.0554; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>polish</t>
+  </si>
+  <si>
+    <t>acc: 0.1468  ± 0.0085; missing: 0.0000  ± 0.0000; f1: 0.1831; macro_f1: 0.1447; mcc: 0.0348</t>
+  </si>
+  <si>
+    <t>taiwan</t>
+  </si>
+  <si>
+    <t>acc: 0.0322  ± 0.0048; missing: 0.0000  ± 0.0000; f1: 0.0020; macro_f1: 0.0312; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>portoseguro</t>
+  </si>
+  <si>
+    <t>acc: 0.3997  ± 0.0100; missing: 0.0038  ± 0.0013; f1: 0.5452; macro_f1: 0.3069; mcc: -0.0166</t>
+  </si>
+  <si>
+    <t>travelinsurance</t>
+  </si>
+  <si>
+    <t>acc: 0.0150  ± 0.0024; missing: 0.0000  ± 0.0000; f1: 0.0004; macro_f1: 0.0148; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>ES_FinanceES</t>
+  </si>
+  <si>
+    <t>acc: 0.1118  ± 0.0040; missing: 0.4290  ± 0.0062; f1: 0.1203; macro_f1: 0.1493; mcc: -0.0693</t>
+  </si>
+  <si>
+    <t>ES_Multifin</t>
+  </si>
+  <si>
+    <t>acc: 0.4043  ± 0.0324; missing: 0.0478  ± 0.0141; f1: 0.4061; macro_f1: 0.3972; mcc: 0.2828</t>
+  </si>
+  <si>
+    <t>ES_EFP</t>
+  </si>
+  <si>
+    <t>acc: 0.2703  ± 0.074; missing: 0.0000  ± 0.000; f1: 0.1150; macro_f1: 0.1418; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>ES_EFPA</t>
+  </si>
+  <si>
+    <t>acc: 0.2544  ± 0.0289; missing: 0.0000  ± 0.0000; f1: 0.1039; macro_f1: 0.1021; mcc: -0.0030</t>
+  </si>
+  <si>
+    <t>ES_FNS</t>
+  </si>
+  <si>
+    <t>ES_TSA</t>
+  </si>
+  <si>
+    <t>acc: 0.0332  ± 0.0029; missing: 0.9363  ± 0.0039; f1: 0.0620; macro_f1: 0.0590; mcc: 0.0465</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen2.5-7B</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.2454</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0018; f1: 0.0279</t>
+  </si>
+  <si>
+    <t>precision: 0; recall: 0; f1: 0</t>
+  </si>
+  <si>
+    <t>acc: 0.6519  ± 0.0051; missing: 0.0000  ± 0.0000; f1: 0.7392; macro_f1: 0.4968; mcc: 0.1926</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0066</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.1461</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0023; f1: 0.0479</t>
+  </si>
+  <si>
+    <t>acc: 0.7608  ± 0.0137; missing: 0.0000  ± 0.0000; f1: 0.7571; macro_f1: 0.7552; mcc: 0.5624</t>
+  </si>
+  <si>
+    <t>acc: 0.3489  ± 0.0312; missing: 0.0085  ± 0.0060; f1: 0.4266; macro_f1:0.3750; mcc: 0.3098</t>
+  </si>
+  <si>
+    <t>rmse: 0.3676; missing: 0.0000  ± 0</t>
+  </si>
+  <si>
+    <t>avg_f1: 0.7488</t>
+  </si>
+  <si>
+    <t>acc: 0.6069  ± 0.022; missing: 0.0000  ± 0.000; f1: 0.5893; macro_f1: 0.5520; mcc: 0.3512</t>
+  </si>
+  <si>
+    <t>acc: 0.4850  ± 0.0161; missing: 0.0000  ± 0.0000; f1: 0.3354; macro_f1: 0.3497; mcc: 0.0602</t>
+  </si>
+  <si>
+    <t>acc: 0.6464  ± 0.0182; missing: 0.0000  ± 0.0000; f1: 0.6261; macro_f1: 0.3586; mcc: 0.1013</t>
+  </si>
+  <si>
+    <t>acc: 0.6081  ± 0.0209; missing: 0.0147  ± 0.0051; f1: 0.6067; macro_f1: 0.5933; mcc: 0.5301</t>
+  </si>
+  <si>
+    <t>acc: 0.7880  ± 0.0183; missing: 0.0000  ± 0.0000; f1: 0.7835; macro_f1: 0.7835; mcc: 0.6015</t>
+  </si>
+  <si>
+    <t>acc: 0.3833  ± 0.0281; missing: 0.0167  ± 0.0074; f1: 0.3327; macro_f1: 0.2946; mcc: 0.3610</t>
+  </si>
+  <si>
+    <t>acc: 0.0009  ± 0.0009</t>
+  </si>
+  <si>
+    <t>acc: 0.1259  ± 0.0081</t>
+  </si>
+  <si>
+    <t>acc: 0.5523  ± 0.013; missing: 0.0000  ± 0.000; f1: 0.3954; macro_f1:0.3586; mcc: 0.0055</t>
+  </si>
+  <si>
+    <t>acc: 0.5065  ± 0.0082; missing: 0.0000  ± 0.0000; f1: 0.4086; macro_f1: 0.4021; mcc: -0.0136</t>
+  </si>
+  <si>
+    <t>acc: 0.5853  ± 0.0146; missing: 0.0000  ± 0.0000; f1: 0.5000; macro_f1: 0.4574; mcc: 0.0683</t>
+  </si>
+  <si>
+    <t>acc: 0.6600  ± 0.0336; missing: 0.0000  ± 0.0000; f1: 0.5248; macro_f1: 0.3976; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.8082  ± 0.0076; missing: 0.0000  ± 0.0000; f1: 0.7225; macro_f1: 0.4470; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.9247  ± 0.0058; missing: 0.0000  ± 0.0000; f1: 0.9219; macro_f1: 0.6336; mcc: 0.2684</t>
+  </si>
+  <si>
+    <t>acc: 0.9447  ± 0.0055; missing: 0.0000  ± 0.0000; f1: 0.9238; macro_f1: 0.5058; mcc: 0.0473</t>
+  </si>
+  <si>
+    <t>acc: 0.9670  ± 0.0048; missing: 0.0000  ± 0.0000; f1: 0.9515; macro_f1: 0.4916; mcc: -0.0049</t>
+  </si>
+  <si>
+    <t>acc: 0.9698  ± 0.0035; missing: 0.0000  ± 0.0000; f1: 0.9549; macro_f1: 0.4923; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.9850  ± 0.0024; missing: 0.0000  ± 0.0000; f1: 0.9776; macro_f1: 0.4962; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.1225  ± 0.0041; missing: 0.3052  ± 0.0058; f1: 0.1172; macro_f1: 0.1531; mcc: -0.1592</t>
+  </si>
+  <si>
+    <t>acc: 0.3609  ± 0.0317; missing: 0.0391  ± 0.0128; f1: 0.3564; macro_f1: 0.3645; mcc: 0.2356</t>
+  </si>
+  <si>
+    <t>acc: 0.3514  ± 0.0796; missing: 0.0000  ± 0.0000; f1: 0.3227; macro_f1: 0.3199; mcc: 0.1158</t>
+  </si>
+  <si>
+    <t>acc: 0.4167  ± 0.0327; missing: 0.0000  ± 0.0000; f1: 0.3931; macro_f1: 0.3998; mcc: 0.2709</t>
+  </si>
+  <si>
+    <t>acc: 0.0136  ± 0.0019; missing: 0.9760  ± 0.0025; f1: 0.0266; macro_f1: 0.0226; mcc: 0.0304</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen2.5-7B-Instruct</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.2558</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0628; f1: 0.1305</t>
+  </si>
+  <si>
+    <t>precision: 0.0052; recall: 0.0141; f1: 0.0076</t>
+  </si>
+  <si>
+    <t>acc: 0.8924  ± 0.0033; missing: 0.0001  ± 0.0001; f1: 0.8919; macro_f1: 0.5614; mcc: 0.1227</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.000; f1: 0.009</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.1137</t>
+  </si>
+  <si>
+    <t>acc: 0.4691  ± 0.016; missing: 0.0247  ± 0.005; f1: 0.4627; macro_f1: 0.5542; mcc: 0.2790</t>
+  </si>
+  <si>
+    <t>acc: 0.1574  ± 0.0238; missing: 0.4809  ± 0.0327; f1: 0.1910; macro_f1: 0.2267; mcc: 0.1271</t>
+  </si>
+  <si>
+    <t>rmse: 0.3041; missing: 0.0000  ± 0</t>
+  </si>
+  <si>
+    <t>avg_f1: 0.5995</t>
+  </si>
+  <si>
+    <t>acc: 0.6250  ± 0.0218; missing: 0.0000  ± 0.0000; f1: 0.6105; macro_f1: 0.5793; mcc: 0.3787</t>
+  </si>
+  <si>
+    <t>acc: 0.5552  ± 0.016; missing: 0.0000  ± 0.000; f1: 0.4483; macro_f1: 0.4357; mcc: 0.1394</t>
+  </si>
+  <si>
+    <t>acc: 0.5029  ± 0.019; missing: 0.0000  ± 0.000; f1: 0.4970; macro_f1: 0.3376; mcc: 0.2531</t>
+  </si>
+  <si>
+    <t>acc: 0.6117  ± 0.0209; missing: 0.0000  ± 0.0000; f1: 0.6193; macro_f1: 0.6011; mcc: 0.5395</t>
+  </si>
+  <si>
+    <t>acc: 0.8480  ± 0.0161; missing: 0.0000  ± 0.0000; f1: 0.8473; macro_f1: 0.8473; mcc: 0.7025</t>
+  </si>
+  <si>
+    <t>acc: 0.3800  ± 0.0281; missing: 0.0067  ± 0.0047; f1: 0.3265; macro_f1: 0.2957; mcc: 0.3546</t>
+  </si>
+  <si>
+    <t>acc: 0.4986  ± 0.013; missing: 0.0000  ± 0.000; f1: 0.4912; macro_f1: 0.4954; mcc: 0.0261</t>
+  </si>
+  <si>
+    <t>acc: 0.5030  ± 0.0082; missing: 0.0000  ± 0.0000; f1: 0.5028; macro_f1: 0.5029; mcc: 0.0071</t>
+  </si>
+  <si>
+    <t>acc: 0.5389  ± 0.0148; missing: 0.0000  ± 0.0000; f1: 0.5329; macro_f1: 0.5158; mcc: 0.0351</t>
+  </si>
+  <si>
+    <t>acc:  0.3700  ± 0.0342; missing:  0.0000  ± 0.0000; f1:  0.3067; macro_f1 0.3464; mcc: -0.0532</t>
+  </si>
+  <si>
+    <t>acc: 0.4892  ± 0.0426; missing: 0.0000  ± 0.0000; f1: 0.4078; macro_f1: 0.4323; mcc: 0.1323</t>
+  </si>
+  <si>
+    <t>acc: 0.5760  ± 0.0095; missing: 0.0000  ± 0.0000; f1: 0.6211; macro_f1: 0.5207; mcc: 0.1441</t>
+  </si>
+  <si>
+    <t>acc: 0.9495  ± 0.0046; missing: 0.0000  ± 0.0000; f1: 0.9729; macro_f1: 0.5039; mcc: 0.1017</t>
+  </si>
+  <si>
+    <t>acc: 0.8136  ± 0.0085; missing: 0.0000  ± 0.0000; f1: 0.8587; macro_f1: 0.6094; mcc: 0.3347</t>
+  </si>
+  <si>
+    <t>acc: 0.9096  ± 0.0069; missing: 0.0000  ± 0.0000; f1: 0.9121; macro_f1: 0.5608; mcc: 0.1219</t>
+  </si>
+  <si>
+    <t>acc: 0.9678  ± 0.0048; missing: 0.0000  ± 0.0000; f1: 0.9519; macro_f1: 0.4918; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.8627  ± 0.0071; missing: 0.0000  ± 0.0000; f1: 0.8995; macro_f1: 0.4863; mcc: -0.0015</t>
+  </si>
+  <si>
+    <t>acc:  0.2626  ± 0.0055; missing:  0.0403  ± 0.0025; f1:  0.2665; macro_f1 0.2521; mcc: -0.1222</t>
+  </si>
+  <si>
+    <t>acc: 0.4652  ± 0.0330; missing: 0.0609  ± 0.0158; f1: 0.4871; macro_f1: 0.4930; mcc: 0.3565</t>
+  </si>
+  <si>
+    <t>acc: 0.2544  ± 0.0289; missing: 0.0000  ± 0.0000; f1: 0.1032; macro_f1: 0.1014; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.0614  ± 0.0039; missing: 0.8470  ± 0.0058; f1: 0.1046; macro_f1: 0.1174; mcc: 0.0819</t>
+  </si>
+  <si>
+    <t>mistralai/Mistral-7B-Instruct-v0.3</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.1483</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0035; f1: 0.0061</t>
+  </si>
+  <si>
+    <t>acc: 0.7979  ± 0.0043; missing: 0.0002  ± 0.0002; f1: 0.8384; macro_f1: 0.5368; mcc: 0.1186</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0094</t>
+  </si>
+  <si>
+    <t>acc: 0.6619  ± 0.0152; missing: 0.0000  ± 0.0000; f1: 0.6704; macro_f1: 0.6972; mcc: 0.4652</t>
+  </si>
+  <si>
+    <t>acc: 0.6170  ± 0.0318; missing: 0.0000  ± 0.0000; f1: 0.6622; macro_f1: 0.5394; mcc: 0.4461</t>
+  </si>
+  <si>
+    <t>rmse: 0.2775; missing: 0.0000  ± 0</t>
+  </si>
+  <si>
+    <t>avg_f1: 0.6853</t>
+  </si>
+  <si>
+    <t>acc: 0.5363  ± 0.0224; missing: 0.0000  ± 0.0000; f1: 0.4279: macro_f1: 0.3513; mcc: 0.2045</t>
+  </si>
+  <si>
+    <t>acc: 0.4716  ± 0.0160; missing: 0.0114  ± 0.0034; f1: 0.3710; macro_f1: 0.3824; mcc: -0.0094</t>
+  </si>
+  <si>
+    <t>acc: 0.6594  ± 0.0181; missing: 0.0000  ± 0.0000; f1: 0.6604; macro_f1: 0.4005; mcc: 0.2106</t>
+  </si>
+  <si>
+    <t>acc: 0.5678  ± 0.0212; missing: 0.0220  ± 0.0063; f1: 0.5494; macro_f1: 0.5460; mcc: 0.4848</t>
+  </si>
+  <si>
+    <t>acc: 0.8420  ± 0.0163; missing: 0.0000  ± 0.0000; f1: 0.8417; macro_f1: 0.8417; mcc: 0.6864</t>
+  </si>
+  <si>
+    <t>acc: 0.3800  ± 0.0281; missing: 0.0433  ± 0.0118; f1: 0.3313; macro_f1: 0.3013; mcc: 0.3587</t>
+  </si>
+  <si>
+    <t>acc 0.0174  ± 0.0032</t>
+  </si>
+  <si>
+    <t>acc 0  ± 0</t>
+  </si>
+  <si>
+    <t>acc: 0.5503  ± 0.013; missing: 0.0000  ± 0.000; f1: 0.5399; macro_f1: 0.5450; mcc: 0.1421</t>
+  </si>
+  <si>
+    <t>acc: 0.5110  ± 0.0082; missing: 0.0000  ± 0.0000; f1: 0.5093; macro_f1: 0.5099; mcc: 0.0253</t>
+  </si>
+  <si>
+    <t>acc: 0.4952  ± 0.0148; missing: 0.0000  ± 0.0000; f1: 0.4936; macro_f1: 0.4950; mcc: 0.0230</t>
+  </si>
+  <si>
+    <t>acc: 0.3350  ± 0.0335; missing: 0.0000  ± 0.0000; f1: 0.2241; macro_f1: 0.2848; mcc: -0.1162</t>
+  </si>
+  <si>
+    <t>acc: 0.4317  ± 0.0422; missing: 0.0000  ± 0.0000; f1: 0.3628; macro_f1: 0.3857; mcc: -0.0598</t>
+  </si>
+  <si>
+    <t>acc: 0.5478  ± 0.0096; missing: 0.0000  ± 0.0000; f1: 0.5935; macro_f1: 0.5118; mcc: 0.1797</t>
+  </si>
+  <si>
+    <t>acc: 0.0500  ± 0.0046; missing: 0.0000  ± 0.0000; f1: 0.0929; macro_f1: 0.0479; mcc: 0.0082</t>
+  </si>
+  <si>
+    <t>acc: 0.1973  ± 0.0087; missing: 0.0000  ± 0.0000; f1: 0.2592; macro_f1: 0.1897; mcc: 0.0066</t>
+  </si>
+  <si>
+    <t>acc: 0.7588  ± 0.0103; missing: 0.0000  ± 0.0000; f1: 0.8237; macro_f1: 0.5162; mcc: 0.1379</t>
+  </si>
+  <si>
+    <t>acc: 0.8132  ± 0.0106; missing: 0.0000  ± 0.0000; f1: 0.8689; macro_f1: 0.4671; mcc: 0.0239</t>
+  </si>
+  <si>
+    <t>acc: 0.0563  ± 0.0047; missing: 0.0000  ± 0.0000; f1: 0.0548; macro_f1: 0.0563; mcc: -0.0139</t>
+  </si>
+  <si>
+    <t>acc: 0.0450  ± 0.0041; missing: 0.0000  ± 0.0000; f1: 0.0587; macro_f1: 0.0448; mcc: 0.0217</t>
+  </si>
+  <si>
+    <t>acc: 0.1909  ± 0.0049; missing: 0.0473  ± 0.0027; f1: 0.1942; macro_f1: 0.1968; mcc: -0.3973</t>
+  </si>
+  <si>
+    <t>acc: 0.3652  ± 0.0318; missing: 0.0130  ± 0.0075; f1: 0.3167; macro_f1: 0.3270; mcc: 0.2504</t>
+  </si>
+  <si>
+    <t>acc: 0.2588  ± 0.0291; missing: 0.0000  ± 0.0000; f1: 0.1133; macro_f1: 0.1102; mcc: 0.0269</t>
+  </si>
+  <si>
+    <t>acc: 0.5040  ± 0.0081; missing: 0.3202  ± 0.0075; f1: 0.5994; macro_f1: 0.4464; mcc: 0.3248</t>
+  </si>
+  <si>
+    <t>meta-llama/Llama-3.2-11B-Vision-Instruct</t>
+  </si>
+  <si>
+    <t>infly/OpenCoder-8B-Instruct</t>
+  </si>
+  <si>
+    <t>CohereForAI/aya-expanse-8b</t>
+  </si>
+  <si>
+    <t>numind/NuExtract-large</t>
+  </si>
+  <si>
+    <t>AIDC-AI/Marco-o1</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0608</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0268; f1: 0.0966</t>
+  </si>
+  <si>
+    <t>precision: 0.0017; recall: 0.0043; f1: 0.0024</t>
+  </si>
+  <si>
+    <t>acc: 0.7863 ± 0.0044; missing: 0.0001 ± 0.0001; f1: 0.8333; macro_f1: 0.5551; mcc: 0.1825</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0012</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.000; f1: 0.041</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0023; f1: 0.0328</t>
+  </si>
+  <si>
+    <t>acc: 0.7186 ± 0.0144; missing: 0.0093 ± 0.0031; f1: 0.7038; macro_f1: 0.6814; mcc: 0.4591</t>
+  </si>
+  <si>
+    <t>acc: 0.1872 ± 0.0255; missing: 0.3191 ± 0.0305; f1: 0.2255; macro_f1: 0.2318; mcc: 0.1146</t>
+  </si>
+  <si>
+    <t>rmse: 0.3736; missing: 0.0000 ± 0</t>
+  </si>
+  <si>
+    <t>acc: 0.6230 ± 0.0218; missing: 0.0000 ± 0.0000; f1: 0.5856; macro_f1: 0.5451; mcc: 0.3779</t>
+  </si>
+  <si>
+    <t>acc: 0.5531 ± 0.016; missing: 0.0000 ± 0.000; f1: 0.4405; macro_f1: 0.4275; mcc: 0.1379</t>
+  </si>
+  <si>
+    <t>acc: 0.4768 ± 0.019; missing: 0.0000 ± 0.000; f1: 0.4725; macro_f1: 0.3203; mcc: 0.1850</t>
+  </si>
+  <si>
+    <t>acc: 0.6062 ± 0.0209; missing: 0.0018 ± 0.0018; f1: 0.5985; macro_f1: 0.5955; mcc: 0.5279</t>
+  </si>
+  <si>
+    <t>0.8440 ± 0.0162; missing: 0.0000 ± 0.0000; f1: 0.8439; macro_f1: 0.8439; mcc: 0.6888</t>
+  </si>
+  <si>
+    <t>acc: 0.4000 ± 0.0283; missing: 0.0200 ± 0.0081; f1: 0.3607; macro_f1: 0.3275; mcc: 0.3768</t>
+  </si>
+  <si>
     <t>acc: 0 ± 0</t>
   </si>
   <si>
-    <t>TATQA</t>
-  </si>
-  <si>
-    <t>acc: 0.0036 ± 0.0015</t>
-  </si>
-  <si>
-    <t>Regulations</t>
-  </si>
-  <si>
-    <t>ConvFinQA</t>
-  </si>
-  <si>
-    <t>EDTSUM</t>
-  </si>
-  <si>
-    <t>Can't get BARTScore; unpickling error</t>
-  </si>
-  <si>
-    <t>ECTSUM</t>
-  </si>
-  <si>
-    <t>BigData22</t>
-  </si>
-  <si>
-    <t>acc: 0.4674 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.3794; macro_f1: 0.4004; mcc: 0.0248</t>
-  </si>
-  <si>
-    <t>ACL18</t>
-  </si>
-  <si>
-    <t>acc: 0.4978 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4915; macro_f1: 0.4928; mcc: 0.0015</t>
-  </si>
-  <si>
-    <t>CIKM18</t>
-  </si>
-  <si>
-    <t>acc: 0.5241 ± 0.0148; missing: 0.0000 ± 0.0000; f1: 0.5194; macro_f1: 0.5027; mcc: 0.0075</t>
-  </si>
-  <si>
-    <t>German</t>
-  </si>
-  <si>
-    <t>acc: 0.3950 ± 0.0347; missing: 0.0000 ± 0.0000; f1: 0.3270; macro_f1: 0.3685; mcc: 0.0364</t>
-  </si>
-  <si>
-    <t>Australian</t>
+    <t>acc: 0.0006 ± 0.0006</t>
+  </si>
+  <si>
+    <t>acc: 0.5632 ± 0.0129; missing: 0.0000 ± 0.0000; f1: 0.5351; macro_f1: 0.5201; mcc: 0.0863</t>
+  </si>
+  <si>
+    <t>acc: 0.5118 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4381; macro_f1: 0.4326; mcc: 0.0073</t>
+  </si>
+  <si>
+    <t>acc: 0.5722 ± 0.0146; missing: 0.0000 ± 0.0000; f1: 0.4797; macro_f1: 0.4345; mcc: 0.0194</t>
+  </si>
+  <si>
+    <t>acc:  0.4750 ± 0.0354; missing:  0.0000 ± 0.0000; f1:  0.4870; macro_f1:  0.4691; mcc: -0.0157</t>
+  </si>
+  <si>
+    <t>acc:  0.4173 ± 0.042; missing:  0.0000 ± 0.000; f1:  0.3322; macro_f1:  0.3587; mcc: -0.0965</t>
+  </si>
+  <si>
+    <t>acc: 0.5466 ± 0.0096; missing: 0.0000 ± 0.0000; f1: 0.5908; macro_f1: 0.5170; mcc: 0.2146</t>
+  </si>
+  <si>
+    <t>acc: 0.9987 ± 0.0008; missing: 0.0000 ± 0.0000; f1: 0.9980; macro_f1: 0.4997; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.7140 ± 0.0099; missing: 0.0000 ± 0.0000; f1: 0.7898; macro_f1: 0.5419; mcc: 0.2834</t>
+  </si>
+  <si>
+    <t>acc:  0.9482 ± 0.0053; missing:  0.0000 ± 0.0000; f1:  0.9235; macro_f1:  0.4867; mcc: -0.0056</t>
+  </si>
+  <si>
+    <t>acc: 0.9678 ± 0.0048; missing: 0.0000 ± 0.0000; f1: 0.9519; macro_f1: 0.4918; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.8279 ± 0.0075; missing: 0.0000 ± 0.0000; f1: 0.8925; macro_f1: 0.4747; mcc: 0.0326</t>
+  </si>
+  <si>
+    <t>acc:  0.1609 ± 0.0046; missing:  0.1654 ± 0.0047; f1:  0.1621; macro_f1:  0.1787; mcc: -0.1642</t>
+  </si>
+  <si>
+    <t>acc: 0.3783 ± 0.0320; missing: 0.0652 ± 0.0163; f1: 0.3806; macro_f1: 0.3905; mcc: 0.2618</t>
+  </si>
+  <si>
+    <t>acc: 0.2703 ± 0.074; missing: 0.0000 ± 0.000; f1: 0.1150; macro_f1: 0.1418; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.2544 ± 0.0289; missing: 0.0000 ± 0.0000; f1: 0.1032; macro_f1: 0.1014; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.0316 ± 0.0028; missing: 0.9415 ± 0.0038; f1: 0.0597; macro_f1: 0.0606; mcc: 0.0583</t>
+  </si>
+  <si>
+    <t>allenai/OLMo-2-1124-7B-Instruct</t>
+  </si>
+  <si>
+    <t>openGPT-X/Teuken-7B-instruct-research-v0.4</t>
+  </si>
+  <si>
+    <t>nvidia/Hymba-1.5B-Instruct</t>
+  </si>
+  <si>
+    <t>tiiuae/falcon-7b-instruct</t>
+  </si>
+  <si>
+    <t>entity_f1: 0</t>
+  </si>
+  <si>
+    <t>acc: 0.1044 ± 0.0033; missing: 0.0032 ± 0.0006; f1: 0.0822; macro_f1: 0.1039; mcc: 0.0488</t>
+  </si>
+  <si>
+    <t>acc: 0.6443 ± 0.0154; missing: 0.0000 ± 0.0000; f1: 0.6435; macro_f1: 0.6085; mcc: 0.3964</t>
+  </si>
+  <si>
+    <t>acc: 0.7660 ± 0.0277; missing: 0.0000 ± 0.0000; f1: 0.7446; macro_f1: 0.5557; mcc: 0.5419</t>
+  </si>
+  <si>
+    <t>rmse: 0.4105; missing: 0.0053 ± 0.0031</t>
+  </si>
+  <si>
+    <t>avg_f1: 0.4471</t>
+  </si>
+  <si>
+    <t>acc:  0.2984 ± 0.0206; missing: 0.0000 ± 0.0000; f1: 0.2887; macro_f1: 0.2962; mcc: -0.0192</t>
+  </si>
+  <si>
+    <t>acc:  0.3416 ± 0.0152; missing: 0.2848 ± 0.0145; f1: 0.3729; macro_f1: 0.3782; mcc: -0.0133</t>
+  </si>
+  <si>
+    <t>acc:  0.6899 ± 0.0176; missing: 0.0000 ± 0.0000; f1: 0.5703; macro_f1: 0.2722; mcc: -0.0599</t>
+  </si>
+  <si>
+    <t>acc: 0.2857 ± 0.0194; missing: 0.0275 ± 0.0070; f1: 0.1911; macro_f1: 0.2205; mcc: 0.1746</t>
+  </si>
+  <si>
+    <t>acc: 0.5040 ± 0.0224; missing: 0.0000 ± 0.0000; f1: 0.3490; macro_f1: 0.3490; mcc: 0.0367</t>
+  </si>
+  <si>
+    <t>acc: 0.0500 ± 0.0126; missing: 0.1733 ± 0.0219; f1: 0.0517; macro_f1: 0.0302; mcc: 0.0538</t>
+  </si>
+  <si>
+    <t>acc: 0.0017 ± 0.0012</t>
+  </si>
+  <si>
+    <t>acc: 0.0659 ± 0.0061</t>
+  </si>
+  <si>
+    <t>acc: 0.5523 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.3930; macro_f1: 0.3558; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc:  0.5062 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4553; macro_f1: 0.4508; mcc: -0.0042</t>
+  </si>
+  <si>
+    <t>acc:  0.4366 ± 0.0147; missing: 0.0000 ± 0.0000; f1: 0.3588; macro_f1: 0.3870; mcc: -0.0128</t>
+  </si>
+  <si>
+    <t>acc: 0.6600 ± 0.0336; missing: 0.0000 ± 0.0000; f1: 0.5248; macro_f1: 0.3976; mcc: 0.0000</t>
   </si>
   <si>
     <t>acc: 0.4317 ± 0.0422; missing: 0.0000 ± 0.0000; f1: 0.2603; macro_f1: 0.3015; mcc: 0.0000</t>
   </si>
   <si>
-    <t>LendingClub</t>
-  </si>
-  <si>
-    <t>acc: 0.1918 ± 0.0076; missing: 0.0000 ± 0.0000; f1: 0.0617; macro_f1: 0.1609; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>ccf</t>
-  </si>
-  <si>
-    <t>acc: 0.9987 ± 0.0008; missing: 0.0000 ± 0.0000; f1: 0.9980; macro_f1: 0.4997; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>ccfraud</t>
+    <t>acc: 0.8082 ± 0.0076; missing: 0.0000 ± 0.0000; f1: 0.7225; macro_f1: 0.4470; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc:  0.9798 ± 0.0029; missing: 0.0000 ± 0.0000; f1: 0.9885; macro_f1: 0.4949; mcc: -0.0050</t>
+  </si>
+  <si>
+    <t>acc:  0.5510 ± 0.0109; missing: 0.0000 ± 0.0000; f1: 0.6682; macro_f1: 0.3675; mcc: -0.1512</t>
+  </si>
+  <si>
+    <t>acc: 0.9488 ± 0.0053; missing: 0.0000 ± 0.0000; f1: 0.9238; macro_f1: 0.4869; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.9698 ± 0.0035; missing: 0.0000 ± 0.0000; f1: 0.9549; macro_f1: 0.4923; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.5592 ± 0.0099; missing: 0.0000 ± 0.0000; f1: 0.7029; macro_f1: 0.3827; mcc: 0.0906</t>
+  </si>
+  <si>
+    <t>acc:  0.0418 ± 0.0025; missing: 0.5570 ± 0.0062; f1: 0.0316; macro_f1: 0.0558; mcc: -0.0178</t>
+  </si>
+  <si>
+    <t>acc: 0.0478 ± 0.0141; missing: 0.9174 ± 0.0182; f1: 0.0817; macro_f1: 0.0789; mcc: 0.0936</t>
+  </si>
+  <si>
+    <t>acc:  0.2973 ± 0.0762; missing: 0.0000 ± 0.0000; f1: 0.2674; macro_f1: 0.2712; mcc: -0.0489</t>
+  </si>
+  <si>
+    <t>acc:  0.2807 ± 0.0298; missing: 0.0088 ± 0.0062; f1: 0.1833; macro_f1: 0.1644; mcc: -0.0007</t>
+  </si>
+  <si>
+    <t>acc:  0.1907 ± 0.0063; missing: 0.6754 ± 0.0076; f1: 0.2616; macro_f1: 0.1599; mcc: -0.0034</t>
+  </si>
+  <si>
+    <t>NousResearch/Hermes-3-Llama-3.1-8B</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0176; f1: 0.0465</t>
+  </si>
+  <si>
+    <t>precision: 0.0017; recall: 0.0043; f1: 0.0025</t>
+  </si>
+  <si>
+    <t>acc: 0.7503 ± 0.0047; missing: 0.0002 ± 0.0002; f1: 0.8089; macro_f1: 0.5263; mcc: 0.1399</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0024</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.000; f1: 0.028</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0045; f1: 0.0269</t>
+  </si>
+  <si>
+    <t>acc: 0.7206 ± 0.0144; missing: 0.0000 ± 0.0000; f1: 0.7265; macro_f1: 0.7350; mcc: 0.5278</t>
+  </si>
+  <si>
+    <t>acc: 0.7277 ± 0.0291; missing: 0.0000 ± 0.0000; f1: 0.7678; macro_f1: 0.6251; mcc: 0.5679</t>
+  </si>
+  <si>
+    <t>rmse: 0.3133; missing: 0.0000 ± 0</t>
+  </si>
+  <si>
+    <t>acc: 0.6190 ± 0.0218; missing: 0.0000 ± 0.0000; f1: 0.6149; macro_f1: 0.5980; mcc: 0.3998</t>
+  </si>
+  <si>
+    <t>acc: 0.5562 ± 0.0160; missing: 0.0021 ± 0.0015; f1: 0.5205; macro_f1: 0.5134; mcc: 0.1049</t>
+  </si>
+  <si>
+    <t>acc:  0.6449 ± 0.0182; missing: 0.0000 ± 0.0000; f1: 0.5829; macro_f1: 0.3304; mcc: -0.0046</t>
+  </si>
+  <si>
+    <t>acc: 0.5989 ± 0.021; missing: 0.0000 ± 0.000; f1: 0.5892; macro_f1: 0.5694; mcc: 0.5171</t>
+  </si>
+  <si>
+    <t>acc: 0.8280 ± 0.0169; missing: 0.0000 ± 0.0000; f1: 0.8264; macro_f1: 0.8264; mcc: 0.6684</t>
+  </si>
+  <si>
+    <t>acc: 0.4000 ± 0.0283; missing: 0.0033 ± 0.0033; f1: 0.3520; macro_f1: 0.3166; mcc: 0.3759</t>
+  </si>
+  <si>
+    <t>acc: 0.5217 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.5206; macro_f1: 0.5143; mcc: 0.0290</t>
+  </si>
+  <si>
+    <t>acc:  0.4997 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4780; macro_f1: 0.4750; mcc: -0.0121</t>
+  </si>
+  <si>
+    <t>acc:  0.5407 ± 0.0147; missing: 0.0000 ± 0.0000; f1: 0.5029; macro_f1: 0.4721; mcc: -0.0111</t>
+  </si>
+  <si>
+    <t>acc:  0.3300 ± 0.0333; missing: 0.0000 ± 0.0000; f1: 0.1931; macro_f1: 0.2637; mcc: -0.1228</t>
+  </si>
+  <si>
+    <t>acc:  0.4101 ± 0.0419; missing: 0.0000 ± 0.0000; f1: 0.4064; macro_f1: 0.4093; mcc: -0.1562</t>
+  </si>
+  <si>
+    <t>acc: 0.5515 ± 0.0096; missing: 0.0000 ± 0.0000; f1: 0.5987; macro_f1: 0.5033; mcc: 0.1258</t>
+  </si>
+  <si>
+    <t>acc: 0.1101 ± 0.0066; missing: 0.0000 ± 0.0000; f1: 0.1963; macro_f1: 0.0997; mcc: 0.0127</t>
+  </si>
+  <si>
+    <t>acc:  0.7183 ± 0.0098; missing: 0.0000 ± 0.0000; f1: 0.7894; macro_f1: 0.4545; mcc: -0.0295</t>
+  </si>
+  <si>
+    <t>acc: 0.4362 ± 0.0102; missing: 0.0000 ± 0.0000; f1: 0.5813; macro_f1: 0.3282; mcc: 0.0052</t>
+  </si>
+  <si>
+    <t>acc: 0.0150 ± 0.0024; missing: 0.0000 ± 0.0000; f1: 0.0004; macro_f1: 0.0148; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc:  0.1779 ± 0.0048; missing: 0.1697 ± 0.0047; f1: 0.1887; macro_f1: 0.1826; mcc: -0.3001</t>
+  </si>
+  <si>
+    <t>acc: 0.4739 ± 0.0330; missing: 0.0130 ± 0.0075; f1: 0.4436; macro_f1: 0.4479; mcc: 0.3644</t>
+  </si>
+  <si>
+    <t>acc: 0.2632 ± 0.0292; missing: 0.0000 ± 0.0000; f1: 0.1283; macro_f1: 0.1259; mcc: 0.0463</t>
+  </si>
+  <si>
+    <t>acc: 0.1131 ± 0.0051; missing: 0.8362 ± 0.0060; f1: 0.1945; macro_f1: 0.1367; mcc: 0.0784</t>
+  </si>
+  <si>
+    <t>bigcode/starcoder2-7b</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0644</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0172; f1: 0.0343</t>
+  </si>
+  <si>
+    <t>precision: 0.0038; recall: 0.0076; f1: 0.0050</t>
+  </si>
+  <si>
+    <t>acc: 0.7813 ± 0.0045; missing: 0.0046 ± 0.0007; f1: 0.8286; macro_f1: 0.5351; mcc: 0.1268</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.000; f1: 0.002</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0086</t>
+  </si>
+  <si>
+    <t>acc: 0.5041 ± 0.0161; missing: 0.0052 ± 0.0023; f1: 0.4614; macro_f1: 0.5139; mcc: 0.3860</t>
+  </si>
+  <si>
+    <t>acc: 0.4000 ± 0.032; missing: 0.0000 ± 0.000; f1: 0.3169; macro_f1: 0.2545; mcc: 0.1487</t>
+  </si>
+  <si>
+    <t>rmse: 0.3693; missing: 0.0000 ± 0</t>
+  </si>
+  <si>
+    <t>acc: 0.3448 ± 0.0214; missing: 0.0081 ± 0.0040; f1: 0.3466; macro_f1: 0.3236; mcc: 0.0124</t>
+  </si>
+  <si>
+    <t>acc: 0.0867 ± 0.009; missing: 0.8328 ± 0.012; f1: 0.1351; macro_f1: 0.1406; mcc: 0.0166</t>
+  </si>
+  <si>
+    <t>acc: 0.3913 ± 0.0186; missing: 0.0029 ± 0.0020; f1: 0.4620; macro_f1: 0.2636; mcc: 0.0354</t>
+  </si>
+  <si>
+    <t>acc: 0.3663 ± 0.0206; missing: 0.0201 ± 0.0060; f1: 0.3183; macro_f1: 0.2985; mcc: 0.2347</t>
+  </si>
+  <si>
+    <t>acc:  0.4980 ± 0.0224; missing: 0.0000 ± 0.0000; f1: 0.3525; macro_f1: 0.3525; mcc: -0.0126</t>
+  </si>
+  <si>
+    <t>acc: 0.1533 ± 0.0208; missing: 0.4933 ± 0.0289; f1: 0.1366; macro_f1: 0.0926; mcc: 0.1577</t>
+  </si>
+  <si>
+    <t>acc: 0.5306 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.4911; macro_f1: 0.4729; mcc: 0.0035</t>
+  </si>
+  <si>
+    <t>acc:  0.5013 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4881; macro_f1: 0.4858; mcc: -0.0059</t>
+  </si>
+  <si>
+    <t>acc:  0.4829 ± 0.0148; missing: 0.0000 ± 0.0000; f1: 0.4851; macro_f1: 0.4824; mcc: -0.0185</t>
+  </si>
+  <si>
+    <t>acc:  0.8591 ± 0.0073; missing: 0.0000 ± 0.0000; f1: 0.9230; macro_f1: 0.4621; mcc: -0.0146</t>
   </si>
   <si>
     <t>acc: 0.0586 ± 0.0051; missing: 0.0000 ± 0.0000; f1: 0.0065; macro_f1: 0.0554; mcc: 0.0000</t>
   </si>
   <si>
-    <t>polish</t>
-  </si>
-  <si>
-    <t>acc: 0.1468 ± 0.0085; missing: 0.0000 ± 0.0000; f1: 0.1831; macro_f1: 0.1447; mcc: 0.0348</t>
-  </si>
-  <si>
-    <t>taiwan</t>
-  </si>
-  <si>
-    <t>acc: 0.0322 ± 0.0048; missing: 0.0000 ± 0.0000; f1: 0.0020; macro_f1: 0.0312; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>portoseguro</t>
-  </si>
-  <si>
-    <t>acc: 0.3997 ± 0.0100; missing: 0.0038 ± 0.0013; f1: 0.5452; macro_f1: 0.3069; mcc: -0.0166</t>
-  </si>
-  <si>
-    <t>travelinsurance</t>
-  </si>
-  <si>
-    <t>acc: 0.0150 ± 0.0024; missing: 0.0000 ± 0.0000; f1: 0.0004; macro_f1: 0.0148; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>ES_FinanceES</t>
-  </si>
-  <si>
-    <t>acc: 0.1118 ± 0.0040; missing: 0.4290 ± 0.0062; f1: 0.1203; macro_f1: 0.1493; mcc: -0.0693</t>
-  </si>
-  <si>
-    <t>ES_Multifin</t>
-  </si>
-  <si>
-    <t>acc: 0.4043 ± 0.0324; missing: 0.0478 ± 0.0141; f1: 0.4061; macro_f1: 0.3972; mcc: 0.2828</t>
-  </si>
-  <si>
-    <t>ES_EFP</t>
-  </si>
-  <si>
-    <t>acc: 0.2703 ± 0.074; missing: 0.0000 ± 0.000; f1: 0.1150; macro_f1: 0.1418; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>ES_EFPA</t>
-  </si>
-  <si>
-    <t>acc: 0.2544 ± 0.0289; missing: 0.0000 ± 0.0000; f1: 0.1039; macro_f1: 0.1021; mcc: -0.0030</t>
-  </si>
-  <si>
-    <t>ES_FNS</t>
-  </si>
-  <si>
-    <t>ES_TSA</t>
-  </si>
-  <si>
-    <t>acc: 0.0332 ± 0.0029; missing: 0.9363 ± 0.0039; f1: 0.0620; macro_f1: 0.0590; mcc: 0.0465</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen2.5-7B</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.2454</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0018; f1: 0.0279</t>
-  </si>
-  <si>
-    <t>precision: 0; recall: 0; f1: 0</t>
-  </si>
-  <si>
-    <t>acc: 0.6519 ± 0.0051; missing: 0.0000 ± 0.0000; f1: 0.7392; macro_f1: 0.4968; mcc: 0.1926</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0000; f1: 0.0066</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0000; f1: 0.1461</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0023; f1: 0.0479</t>
-  </si>
-  <si>
-    <t>acc: 0.7608 ± 0.0137; missing: 0.0000 ± 0.0000; f1: 0.7571; macro_f1: 0.7552; mcc: 0.5624</t>
-  </si>
-  <si>
-    <t>acc: 0.3489 ± 0.0312; missing: 0.0085 ± 0.0060; f1: 0.4266; macro_f1:0.3750; mcc: 0.3098</t>
-  </si>
-  <si>
-    <t>rmse: 0.3676; missing: 0.0000 ± 0</t>
-  </si>
-  <si>
-    <t>avg_f1: 0.7488</t>
-  </si>
-  <si>
-    <t>acc: 0.6069 ± 0.022; missing: 0.0000 ± 0.000; f1: 0.5893; macro_f1: 0.5520; mcc: 0.3512</t>
-  </si>
-  <si>
-    <t>acc: 0.4850 ± 0.0161; missing: 0.0000 ± 0.0000; f1: 0.3354; macro_f1: 0.3497; mcc: 0.0602</t>
-  </si>
-  <si>
-    <t>acc: 0.6464 ± 0.0182; missing: 0.0000 ± 0.0000; f1: 0.6261; macro_f1: 0.3586; mcc: 0.1013</t>
-  </si>
-  <si>
-    <t>acc: 0.6081 ± 0.0209; missing: 0.0147 ± 0.0051; f1: 0.6067; macro_f1: 0.5933; mcc: 0.5301</t>
-  </si>
-  <si>
-    <t>acc: 0.7880 ± 0.0183; missing: 0.0000 ± 0.0000; f1: 0.7835; macro_f1: 0.7835; mcc: 0.6015</t>
-  </si>
-  <si>
-    <t>acc: 0.3833 ± 0.0281; missing: 0.0167 ± 0.0074; f1: 0.3327; macro_f1: 0.2946; mcc: 0.3610</t>
-  </si>
-  <si>
-    <t>acc: 0.0009 ± 0.0009</t>
-  </si>
-  <si>
-    <t>acc: 0.1259 ± 0.0081</t>
-  </si>
-  <si>
-    <t>acc: 0.5523 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.3954; macro_f1:0.3586; mcc: 0.0055</t>
-  </si>
-  <si>
-    <t>acc: 0.5065 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4086; macro_f1: 0.4021; mcc: -0.0136</t>
-  </si>
-  <si>
-    <t>acc: 0.5853 ± 0.0146; missing: 0.0000 ± 0.0000; f1: 0.5000; macro_f1: 0.4574; mcc: 0.0683</t>
-  </si>
-  <si>
-    <t>acc: 0.6600 ± 0.0336; missing: 0.0000 ± 0.0000; f1: 0.5248; macro_f1: 0.3976; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>acc: 0.8082 ± 0.0076; missing: 0.0000 ± 0.0000; f1: 0.7225; macro_f1: 0.4470; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>acc: 0.9247 ± 0.0058; missing: 0.0000 ± 0.0000; f1: 0.9219; macro_f1: 0.6336; mcc: 0.2684</t>
-  </si>
-  <si>
-    <t>acc: 0.9447 ± 0.0055; missing: 0.0000 ± 0.0000; f1: 0.9238; macro_f1: 0.5058; mcc: 0.0473</t>
-  </si>
-  <si>
-    <t>acc: 0.9670 ± 0.0048; missing: 0.0000 ± 0.0000; f1: 0.9515; macro_f1: 0.4916; mcc: -0.0049</t>
-  </si>
-  <si>
-    <t>acc: 0.9698 ± 0.0035; missing: 0.0000 ± 0.0000; f1: 0.9549; macro_f1: 0.4923; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>acc: 0.9850 ± 0.0024; missing: 0.0000 ± 0.0000; f1: 0.9776; macro_f1: 0.4962; mcc: 0.0000</t>
-  </si>
-  <si>
-    <t>acc: 0.1225 ± 0.0041; missing: 0.3052 ± 0.0058; f1: 0.1172; macro_f1: 0.1531; mcc: -0.1592</t>
-  </si>
-  <si>
-    <t>acc: 0.3609 ± 0.0317; missing: 0.0391 ± 0.0128; f1: 0.3564; macro_f1: 0.3645; mcc: 0.2356</t>
-  </si>
-  <si>
-    <t>acc: 0.3514 ± 0.0796; missing: 0.0000 ± 0.0000; f1: 0.3227; macro_f1: 0.3199; mcc: 0.1158</t>
-  </si>
-  <si>
-    <t>acc: 0.4167 ± 0.0327; missing: 0.0000 ± 0.0000; f1: 0.3931; macro_f1: 0.3998; mcc: 0.2709</t>
-  </si>
-  <si>
-    <t>acc: 0.0136 ± 0.0019; missing: 0.9760 ± 0.0025; f1: 0.0266; macro_f1: 0.0226; mcc: 0.0304</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen2.5-7B-Instruct</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.2558</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0628; f1: 0.1305</t>
-  </si>
-  <si>
-    <t>precision: 0.0052; recall: 0.0141; f1: 0.0076</t>
-  </si>
-  <si>
-    <t>acc: 0.8924 ± 0.0033; missing: 0.0001 ± 0.0001; f1: 0.8919; macro_f1: 0.5614; mcc: 0.1227</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.000; f1: 0.009</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0000; f1: 0.1137</t>
-  </si>
-  <si>
-    <t>acc: 0.4691 ± 0.016; missing: 0.0247 ± 0.005; f1: 0.4627; macro_f1: 0.5542; mcc: 0.2790</t>
-  </si>
-  <si>
-    <t>acc: 0.1574 ± 0.0238; missing: 0.4809 ± 0.0327; f1: 0.1910; macro_f1: 0.2267; mcc: 0.1271</t>
-  </si>
-  <si>
-    <t>rmse: 0.3041; missing: 0.0000 ± 0</t>
-  </si>
-  <si>
-    <t>acc: 0.6250 ± 0.0218; missing: 0.0000 ± 0.0000; f1: 0.6105; macro_f1: 0.5793; mcc: 0.3787</t>
-  </si>
-  <si>
-    <t>acc: 0.5552 ± 0.016; missing: 0.0000 ± 0.000; f1: 0.4483; macro_f1: 0.4357; mcc: 0.1394</t>
-  </si>
-  <si>
-    <t>acc: 0.5029 ± 0.019; missing: 0.0000 ± 0.000; f1: 0.4970; macro_f1: 0.3376; mcc: 0.2531</t>
-  </si>
-  <si>
-    <t>acc: 0.6117 ± 0.0209; missing: 0.0000 ± 0.0000; f1: 0.6193; macro_f1: 0.6011; mcc: 0.5395</t>
-  </si>
-  <si>
-    <t>acc: 0.8480 ± 0.0161; missing: 0.0000 ± 0.0000; f1: 0.8473; macro_f1: 0.8473; mcc: 0.7025</t>
-  </si>
-  <si>
-    <t>acc: 0.3800 ± 0.0281; missing: 0.0067 ± 0.0047; f1: 0.3265; macro_f1: 0.2957; mcc: 0.3546</t>
-  </si>
-  <si>
-    <t>acc: 0.8627 ± 0.0071; missing: 0.0000 ± 0.0000; f1: 0.8995; macro_f1: 0.4863; mcc: -0.0015</t>
-  </si>
-  <si>
-    <t>mistralai/Mistral-7B-Instruct-v0.3</t>
-  </si>
-  <si>
-    <t>entity_f1|0.1483</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0035; f1: 0.0061</t>
-  </si>
-  <si>
-    <t>acc: 0.7979 ± 0.0043; missing: 0.0002 ± 0.0002; f1: 0.8384; macro_f1: 0.5368; mcc: 0.1186</t>
-  </si>
-  <si>
-    <t>entity_f1: 0.0000; f1: 0.0094</t>
-  </si>
-  <si>
-    <t>acc: 0.6619 ± 0.0152; missing: 0.0000 ± 0.0000; f1: 0.6704; macro_f1: 0.6972; mcc: 0.4652</t>
-  </si>
-  <si>
-    <t>acc: 0.6170 ± 0.0318; missing: 0.0000 ± 0.0000; f1: 0.6622; macro_f1: 0.5394; mcc: 0.4461</t>
-  </si>
-  <si>
-    <t>rmse: 0.2775; missing: 0.0000 ± 0</t>
-  </si>
-  <si>
-    <t>avg_f1: 0.6853</t>
-  </si>
-  <si>
-    <t>acc: 0.5363 ± 0.0224; missing: 0.0000 ± 0.0000; f1: 0.4279: macro_f1: 0.3513; mcc: 0.2045</t>
-  </si>
-  <si>
-    <t>acc: 0.4716 ± 0.0160; missing: 0.0114 ± 0.0034; f1: 0.3710; macro_f1: 0.3824; mcc: -0.0094</t>
-  </si>
-  <si>
-    <t>acc: 0.6594 ± 0.0181; missing: 0.0000 ± 0.0000; f1: 0.6604; macro_f1: 0.4005; mcc: 0.2106</t>
-  </si>
-  <si>
-    <t>acc: 0.5678 ± 0.0212; missing: 0.0220 ± 0.0063; f1: 0.5494; macro_f1: 0.5460; mcc: 0.4848</t>
-  </si>
-  <si>
-    <t>acc: 0.8420 ± 0.0163; missing: 0.0000 ± 0.0000; f1: 0.8417; macro_f1: 0.8417; mcc: 0.6864</t>
-  </si>
-  <si>
-    <t>acc: 0.3800 ± 0.0281; missing: 0.0433 ± 0.0118; f1: 0.3313; macro_f1: 0.3013; mcc: 0.3587</t>
-  </si>
-  <si>
-    <t>acc 0.0174 ± 0.0032</t>
-  </si>
-  <si>
-    <t>acc 0 ± 0</t>
-  </si>
-  <si>
-    <t>acc: 0.5503 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.5399; macro_f1: 0.5450; mcc: 0.1421</t>
-  </si>
-  <si>
-    <t>acc: 0.5110 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.5093; macro_f1: 0.5099; mcc: 0.0253</t>
-  </si>
-  <si>
-    <t>acc: 0.4952 ± 0.0148; missing: 0.0000 ± 0.0000; f1: 0.4936; macro_f1: 0.4950; mcc: 0.0230</t>
-  </si>
-  <si>
-    <t>acc: 0.3350 ± 0.0335; missing: 0.0000 ± 0.0000; f1: 0.2241; macro_f1: 0.2848; mcc: -0.1162</t>
-  </si>
-  <si>
-    <t>acc: 0.4317 ± 0.0422; missing: 0.0000 ± 0.0000; f1: 0.3628; macro_f1: 0.3857; mcc: -0.0598</t>
-  </si>
-  <si>
-    <t>acc: 0.5478 ± 0.0096; missing: 0.0000 ± 0.0000; f1: 0.5935; macro_f1: 0.5118; mcc: 0.1797</t>
-  </si>
-  <si>
-    <t>acc: 0.0500 ± 0.0046; missing: 0.0000 ± 0.0000; f1: 0.0929; macro_f1: 0.0479; mcc: 0.0082</t>
-  </si>
-  <si>
-    <t>acc: 0.1973 ± 0.0087; missing: 0.0000 ± 0.0000; f1: 0.2592; macro_f1: 0.1897; mcc: 0.0066</t>
-  </si>
-  <si>
-    <t>acc: 0.7588 ± 0.0103; missing: 0.0000 ± 0.0000; f1: 0.8237; macro_f1: 0.5162; mcc: 0.1379</t>
-  </si>
-  <si>
-    <t>acc: 0.8132 ± 0.0106; missing: 0.0000 ± 0.0000; f1: 0.8689; macro_f1: 0.4671; mcc: 0.0239</t>
-  </si>
-  <si>
-    <t>acc: 0.0563 ± 0.0047; missing: 0.0000 ± 0.0000; f1: 0.0548; macro_f1: 0.0563; mcc: -0.0139</t>
-  </si>
-  <si>
-    <t>acc: 0.0450 ± 0.0041; missing: 0.0000 ± 0.0000; f1: 0.0587; macro_f1: 0.0448; mcc: 0.0217</t>
-  </si>
-  <si>
-    <t>acc: 0.1909 ± 0.0049; missing: 0.0473 ± 0.0027; f1: 0.1942; macro_f1: 0.1968; mcc: -0.3973</t>
-  </si>
-  <si>
-    <t>acc: 0.3652 ± 0.0318; missing: 0.0130 ± 0.0075; f1: 0.3167; macro_f1: 0.3270; mcc: 0.2504</t>
-  </si>
-  <si>
-    <t>acc: 0.2588 ± 0.0291; missing: 0.0000 ± 0.0000; f1: 0.1133; macro_f1: 0.1102; mcc: 0.0269</t>
-  </si>
-  <si>
-    <t>acc: 0.5040 ± 0.0081; missing: 0.3202 ± 0.0075; f1: 0.5994; macro_f1: 0.4464; mcc: 0.3248</t>
-  </si>
-  <si>
-    <t>meta-llama/Llama-3.2-11B-Vision-Instruct</t>
+    <t>acc:  0.1069 ± 0.0039; missing: 0.7596 ± 0.0054; f1: 0.1577; macro_f1: 0.1150; mcc: -0.0068</t>
+  </si>
+  <si>
+    <t>acc: 0.1130 ± 0.0209; missing: 0.7130 ± 0.0299; f1: 0.1603; macro_f1: 0.1635; mcc: 0.0958</t>
+  </si>
+  <si>
+    <t>acc: 0.2588 ± 0.0291; missing: 0.0000 ± 0.0000; f1: 0.1129; macro_f1: 0.1112; mcc: 0.0293</t>
+  </si>
+  <si>
+    <t>acc: 0.0172 ± 0.0021; missing: 0.9700 ± 0.0028; f1: 0.0335; macro_f1: 0.0237; mcc: 0.0163</t>
+  </si>
+  <si>
+    <t>codellama/CodeLlama-7b-Instruct-hf</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.1743</t>
+  </si>
+  <si>
+    <t>precision: 0.0032; recall: 0.0065; f1: 0.0043</t>
+  </si>
+  <si>
+    <t>acc: 0.4219 ± 0.0053; missing: 0.0076 ± 0.0009; f1: 0.5335; macro_f1: 0.3595; mcc: 0.1076</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0002</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0032</t>
+  </si>
+  <si>
+    <t>acc: 0.6340 ± 0.0155; missing: 0.0000 ± 0.0000; f1: 0.6361; macro_f1: 0.6685; mcc: 0.4749</t>
+  </si>
+  <si>
+    <t>acc: 0.6596 ± 0.031; missing: 0.0000 ± 0.000; f1: 0.6570; macro_f1: 0.4878; mcc: 0.4316</t>
+  </si>
+  <si>
+    <t>rmse: 0.3872; missing: 0.0000 ± 0</t>
+  </si>
+  <si>
+    <t>acc: 0.3286 ± 0.0211; missing: 0.0000 ± 0.0000; f1: 0.2946; macro_f1: 0.2746; mcc: 0.0538</t>
+  </si>
+  <si>
+    <t>acc:  0.1950 ± 0.0127; missing: 0.5955 ± 0.0158; f1: 0.2460; macro_f1: 0.2538; mcc: -0.0019</t>
+  </si>
+  <si>
+    <t>acc:  0.6797 ± 0.0178; missing: 0.0000 ± 0.0000; f1: 0.5695; macro_f1: 0.2737; mcc: -0.0090</t>
+  </si>
+  <si>
+    <t>acc: 0.4121 ± 0.0211; missing: 0.0421 ± 0.0086; f1: 0.3620; macro_f1: 0.3406; mcc: 0.3261</t>
+  </si>
+  <si>
+    <t>acc: 0.5540 ± 0.0223; missing: 0.0000 ± 0.0000; f1: 0.4596; macro_f1: 0.4596; mcc: 0.1968</t>
+  </si>
+  <si>
+    <t>acc: 0.2267 ± 0.0242; missing: 0.0500 ± 0.0126; f1: 0.1784; macro_f1: 0.1349; mcc: 0.2055</t>
+  </si>
+  <si>
+    <t>acc: 0.5061 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.5037; macro_f1: 0.5055; mcc: 0.0311</t>
+  </si>
+  <si>
+    <t>acc: 0.5188 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4405; macro_f1: 0.4348; mcc: 0.0276</t>
+  </si>
+  <si>
+    <t>acc:  0.5748 ± 0.0146; missing: 0.0000 ± 0.0000; f1: 0.4471; macro_f1: 0.3934; mcc: -0.0034</t>
+  </si>
+  <si>
+    <t>acc:  0.2579 ± 0.0084; missing: 0.0000 ± 0.0000; f1: 0.2230; macro_f1: 0.2544; mcc: -0.0383</t>
+  </si>
+  <si>
+    <t>acc: 0.0013 ± 0.0008; missing: 0.0000 ± 0.0000; f1: 0.0000; macro_f1: 0.0013; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc: 0.3341 ± 0.0103; missing: 0.0000 ± 0.0000; f1: 0.4384; macro_f1: 0.2982; mcc: 0.1126</t>
+  </si>
+  <si>
+    <t>acc: 0.8676 ± 0.0081; missing: 0.0000 ± 0.0000; f1: 0.8898; macro_f1: 0.5562; mcc: 0.1339</t>
+  </si>
+  <si>
+    <t>acc:  0.2103 ± 0.011; missing: 0.0000 ± 0.000; f1: 0.3111; macro_f1: 0.1894; mcc: -0.0160</t>
+  </si>
+  <si>
+    <t>acc: 0.0302 ± 0.0035; missing: 0.0000 ± 0.0000; f1: 0.0018; macro_f1: 0.0293; mcc: 0.0000</t>
+  </si>
+  <si>
+    <t>acc:  0.1741 ± 0.0048; missing: 0.5694 ± 0.0062; f1: 0.2046; macro_f1: 0.1585; mcc: -0.0258</t>
+  </si>
+  <si>
+    <t>acc: 0.0609 ± 0.0158; missing: 0.8304 ± 0.0248; f1: 0.0940; macro_f1: 0.1005; mcc: 0.0589</t>
+  </si>
+  <si>
+    <t>acc:  0.2703 ± 0.074; missing: 0.0000 ± 0.000; f1: 0.1558; macro_f1: 0.1725; mcc: -0.0282</t>
+  </si>
+  <si>
+    <t>acc: 0.2632 ± 0.0292; missing: 0.0000 ± 0.0000; f1: 0.1288; macro_f1: 0.1260; mcc: 0.0364</t>
+  </si>
+  <si>
+    <t>acc: 0.0666 ± 0.0040; missing: 0.8971 ± 0.0049; f1: 0.1153; macro_f1: 0.0616; mcc: 0.0074</t>
+  </si>
+  <si>
+    <t>utter-project/EuroLLM-9B-Instruct</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.1087</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0086; f1: 0.0411</t>
+  </si>
+  <si>
+    <t>precision: 0.0037; recall: 0.0098; f1: 0.0053</t>
+  </si>
+  <si>
+    <t>acc: 0.2834 ± 0.0049; missing: 0.0001 ± 0.0001; f1: 0.3642; macro_f1: 0.2659; mcc: 0.1239</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0036</t>
+  </si>
+  <si>
+    <t>entity_f1: 0.0000; f1: 0.0047</t>
+  </si>
+  <si>
+    <t>acc: 0.6278 ± 0.0155; missing: 0.0000 ± 0.0000; f1: 0.6285; macro_f1: 0.6733; mcc: 0.4751</t>
+  </si>
+  <si>
+    <t>acc: 0.6170 ± 0.0318; missing: 0.0085 ± 0.0060; f1: 0.6525; macro_f1: 0.5175; mcc: 0.3836</t>
+  </si>
+  <si>
+    <t>rmse: 1.3248; missing: 0.9982 ± 0.0018</t>
+  </si>
+  <si>
+    <t>acc: 0.3891 ± 0.0219; missing: 0.0020 ± 0.0020; f1: 0.4038; macro_f1: 0.3857; mcc: 0.1128</t>
+  </si>
+  <si>
+    <t>acc: 0.5088 ± 0.0161; missing: 0.0227 ± 0.0048; f1: 0.4305; macro_f1: 0.4405; mcc: 0.1137</t>
+  </si>
+  <si>
+    <t>acc: 0.5319 ± 0.0190; missing: 0.0014 ± 0.0014; f1: 0.5592; macro_f1: 0.3414; mcc: 0.0681</t>
+  </si>
+  <si>
+    <t>acc: 0.5403 ± 0.0213; missing: 0.0220 ± 0.0063; f1: 0.5115; macro_f1: 0.5223; mcc: 0.4513</t>
+  </si>
+  <si>
+    <t>acc: 0.5500 ± 0.0223; missing: 0.0020 ± 0.0020; f1: 0.4484; macro_f1: 0.4484; mcc: 0.1971</t>
+  </si>
+  <si>
+    <t>acc: 0.2100 ± 0.0236; missing: 0.0567 ± 0.0134; f1: 0.1689; macro_f1: 0.1461; mcc: 0.1855</t>
+  </si>
+  <si>
+    <t>acc: 0.4552 ± 0.013; missing: 0.0000 ± 0.000; f1: 0.3187; macro_f1: 0.3466; mcc: 0.0168</t>
+  </si>
+  <si>
+    <t>acc:  0.4839 ± 0.0082; missing: 0.0000 ± 0.0000; f1: 0.4068; macro_f1: 0.4121; mcc: -0.0197</t>
+  </si>
+  <si>
+    <t>acc: 0.4724 ± 0.0148; missing: 0.0000 ± 0.0000; f1: 0.4510; macro_f1: 0.4627; mcc: 0.0165</t>
+  </si>
+  <si>
+    <t>acc:  0.8079 ± 0.0076; missing: 0.0000 ± 0.0000; f1: 0.7224; macro_f1: 0.4469; mcc: -0.0094</t>
+  </si>
+  <si>
+    <t>acc: 0.8981 ± 0.0073; missing: 0.0000 ± 0.0000; f1: 0.9009; macro_f1: 0.5048; mcc: 0.0098</t>
+  </si>
+  <si>
+    <t>acc:  0.9201 ± 0.0073; missing: 0.0000 ± 0.0000; f1: 0.9286; macro_f1: 0.4969; mcc: -0.0042</t>
+  </si>
+  <si>
+    <t>acc:  0.1705 ± 0.0047; missing: 0.0366 ± 0.0024; f1: 0.1687; macro_f1: 0.1881; mcc: -0.3087</t>
+  </si>
+  <si>
+    <t>acc: 0.4261 ± 0.0327; missing: 0.0739 ± 0.0173; f1: 0.4411; macro_f1: 0.4551; mcc: 0.3358</t>
+  </si>
+  <si>
+    <t>acc: 0.2998 ± 0.0074; missing: 0.5957 ± 0.0079; f1: 0.4179; macro_f1: 0.2881; mcc: 0.1432</t>
+  </si>
+  <si>
+    <t>EleutherAI/gpt-neo-2.7B</t>
   </si>
 </sst>
 </file>
@@ -524,13 +1128,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -570,18 +1174,20 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -591,6 +1197,42 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -607,6 +1249,22 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -812,350 +1470,2362 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="1"/>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46">
-      <c r="C46" s="5"/>
+      <c r="D45" s="3"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="1"/>
-      <c r="F47" s="1"/>
+      <c r="D47" s="3"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E69" s="1"/>
+      <c r="E69" s="3"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1" t="s">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D81" s="1"/>
-      <c r="F81" s="1"/>
+      <c r="D81" s="3"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1171,339 +3841,338 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="C1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46">
-      <c r="C46" s="5"/>
-    </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="3" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1520,278 +4189,340 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>114</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="A2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>124</v>
+      <c r="C25" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>125</v>
+      <c r="C27" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>126</v>
+      <c r="C29" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>127</v>
+      <c r="C31" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>128</v>
+      <c r="C33" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>129</v>
+      <c r="C35" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="C49" s="3" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="C51" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="C53" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C55" s="3" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C57" s="3" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="C59" s="3" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="C61" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="C63" s="3" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
+      <c r="C65" s="3" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="C67" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>130</v>
+      <c r="C69" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="C71" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="C73" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="C75" s="3" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>72</v>
       </c>
+      <c r="C77" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>74</v>
       </c>
+      <c r="C79" s="3" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1807,340 +4538,339 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="C1" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>132</v>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>133</v>
+      <c r="C5" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>134</v>
+      <c r="C9" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>135</v>
+      <c r="C13" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>136</v>
+      <c r="C17" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>137</v>
+      <c r="C19" s="3" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>138</v>
+      <c r="C21" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>139</v>
+      <c r="C23" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>140</v>
+      <c r="C25" s="3" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>141</v>
+      <c r="C27" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>142</v>
+      <c r="C29" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>143</v>
+      <c r="C31" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>144</v>
+      <c r="C33" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>145</v>
+      <c r="C35" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>146</v>
+      <c r="C39" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>147</v>
+      <c r="C43" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46">
-      <c r="C46" s="5"/>
-    </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>148</v>
+      <c r="C49" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>149</v>
+      <c r="C51" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>150</v>
+      <c r="C53" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>151</v>
+      <c r="C55" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>152</v>
+      <c r="C57" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>153</v>
+      <c r="C59" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>154</v>
+      <c r="C61" s="3" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>155</v>
+      <c r="C63" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>156</v>
+      <c r="C65" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>157</v>
+      <c r="C67" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>158</v>
+      <c r="C69" s="3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>159</v>
+      <c r="C71" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>160</v>
+      <c r="C73" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>161</v>
+      <c r="C75" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>162</v>
+      <c r="C79" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>163</v>
+      <c r="C83" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2156,217 +4886,622 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="3"/>
+      <c r="C1" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="C1" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1"/>
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C13" s="3" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="C15" s="3" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="C17" s="3" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="C19" s="3" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="C21" s="3" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C25" s="3" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="C27" s="3" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="C29" s="3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="C31" s="3" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="C33" s="3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="C35" s="3" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="C37" s="3" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="C39" s="3" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="C43" s="3" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="C45" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="C47" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="C49" s="3" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="C51" s="3" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="C53" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C55" s="3" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C57" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>54</v>
       </c>
+      <c r="C59" s="3" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="C61" s="3" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="C63" s="3" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>60</v>
       </c>
+      <c r="C65" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="C67" s="3" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="C69" s="3" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="C71" s="3" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="C73" s="3" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="C75" s="3" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>72</v>
       </c>
+      <c r="C77" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>74</v>
       </c>
+      <c r="C79" s="3" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>76</v>
       </c>
+      <c r="C81" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>77</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
